--- a/recent_sitemap_outputs/recent_urls.xlsx
+++ b/recent_sitemap_outputs/recent_urls.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,21 +440,41 @@
           <t>scrape_status</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>relevance_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>semantic_match</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>processed_markdown_saved</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>processed_markdown_path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/new-york-auto-show</t>
+          <t>https://www.motortrend.com/rankings/under-75k</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-25T17:50:11Z</t>
+          <t>2026-03-30T16:12:54Z</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000002_new-york-auto-show.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000002_rankings_under-75k.md</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,21 +482,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/archive</t>
+          <t>https://www.motortrend.com/rankings/under-65k</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-25T17:49:12Z</t>
+          <t>2026-03-30T16:14:49Z</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000003_archive.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000003_rankings_under-65k.md</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -484,21 +518,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/</t>
+          <t>https://www.motortrend.com/rankings/under-50k</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-30T15:13:36Z</t>
+          <t>2026-03-30T16:16:14Z</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000004_home.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000004_rankings_under-50k.md</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -506,21 +554,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/best-looking-cars</t>
+          <t>https://www.motortrend.com/rankings/under-45k</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-26T20:38:27Z</t>
+          <t>2026-03-30T16:20:03Z</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000005_features_best-looking-cars.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000005_rankings_under-45k.md</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -528,21 +590,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/best-used-luxury-suvs</t>
+          <t>https://www.motortrend.com/rankings/suvs/luxury/4x4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-26T20:22:48Z</t>
+          <t>2026-03-30T16:08:48Z</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000006_features_best-used-luxury-suvs.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000006_rankings_suvs_luxury_4x4.md</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -550,21 +626,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/best-used-hybrid-suvs</t>
+          <t>https://www.motortrend.com/rankings/suvs/electric/safest</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-26T20:35:44Z</t>
+          <t>2026-03-30T16:05:23Z</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000007_features_best-used-hybrid-suvs.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000007_rankings_suvs_electric_safest.md</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -572,21 +662,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/best-used-suvs-30000</t>
+          <t>https://www.motortrend.com/rankings/suvs/luxury/safest</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-26T20:17:10Z</t>
+          <t>2026-03-30T16:11:48Z</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000008_features_best-used-suvs-30000.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000008_rankings_suvs_luxury_safest.md</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -594,21 +698,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/best-used-3-row-suvs</t>
+          <t>https://www.motortrend.com/rankings/suvs/awd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-26T20:32:15Z</t>
+          <t>2026-03-30T16:24:35Z</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000009_features_best-used-3-row-suvs.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000009_rankings_suvs_awd.md</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -616,21 +734,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/best-used-hybrid-cars</t>
+          <t>https://www.motortrend.com/rankings/sedans/hybrid/awd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-26T20:33:44Z</t>
+          <t>2026-03-30T16:01:42Z</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000010_features_best-used-hybrid-cars.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000010_rankings_sedans_hybrid_awd.md</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -638,21 +770,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/most-reliable-suvs</t>
+          <t>https://www.motortrend.com/rankings/suvs/electric/awd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-25T19:51:42Z</t>
+          <t>2026-03-30T16:03:37Z</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000011_features_most-reliable-suvs.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000011_rankings_suvs_electric_awd.md</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -660,21 +806,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/most-reliable-luxury-suvs</t>
+          <t>https://www.motortrend.com/rankings/suvs/luxury/awd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-26T00:14:18Z</t>
+          <t>2026-03-30T16:10:33Z</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000012_features_most-reliable-luxury-suvs.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000012_rankings_suvs_luxury_awd.md</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -682,21 +842,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/gear-reviews/amazon-spring-sale-2026-best-automotive-deals</t>
+          <t>https://www.motortrend.com/new-york-auto-show</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-26T18:35:30Z</t>
+          <t>2026-03-25T17:50:11Z</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000013_gear-reviews_amazon-spring-sale-2026-best-automotive-deals.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000013_new-york-auto-show.md</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -704,21 +878,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/yearlong-review-update-3-2025-acura-adx-engine-stop-start</t>
+          <t>https://www.motortrend.com/archive</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-27T09:10:12Z</t>
+          <t>2026-03-25T17:49:12Z</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000014_reviews_yearlong-review-update-3-2025-acura-adx-engine-stop-start.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000014_archive.md</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -726,21 +914,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/yearlong-review-update-6-2025-toyota-land-crusier-how-to-drive</t>
+          <t>https://www.motortrend.com/</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-27T12:10:35Z</t>
+          <t>2026-03-30T15:13:36Z</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000015_reviews_yearlong-review-update-6-2025-toyota-land-crusier-how-to-drive.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000015_home.md</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -748,21 +950,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/us-spec-first-look-nissan-z-nismo-manual</t>
+          <t>https://www.motortrend.com/features/best-looking-cars</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-25T17:47:28Z</t>
+          <t>2026-03-26T20:38:27Z</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000016_news_us-spec-first-look-nissan-z-nismo-manual.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000016_features_best-looking-cars.md</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -770,21 +986,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/2027-chevrolet-corvette-grand-sport-preview</t>
+          <t>https://www.motortrend.com/features/best-used-luxury-suvs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-26T18:04:53Z</t>
+          <t>2026-03-26T20:22:48Z</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000017_news_2027-chevrolet-corvette-grand-sport-preview.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000017_features_best-used-luxury-suvs.md</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -792,21 +1022,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/first-test-2025-ford-bronco-rtr-rovr</t>
+          <t>https://www.motortrend.com/features/best-used-hybrid-suvs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-25T15:40:12Z</t>
+          <t>2026-03-26T20:35:44Z</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000018_reviews_first-test-2025-ford-bronco-rtr-rovr.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000018_features_best-used-hybrid-suvs.md</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -814,21 +1058,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/yearlong-review-update-2-2025-hyundai-santa-fe-hybrid-limited-awd-winter</t>
+          <t>https://www.motortrend.com/features/best-used-suvs-30000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-30T14:58:52Z</t>
+          <t>2026-03-26T20:17:10Z</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000019_reviews_yearlong-review-update-2-2025-hyundai-santa-fe-hybrid-limited-awd-winter.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000019_features_best-used-suvs-30000.md</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -836,21 +1094,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/first-test-2026-ford-mustang-rtr-spec-5</t>
+          <t>https://www.motortrend.com/features/best-used-3-row-suvs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-27T09:10:15Z</t>
+          <t>2026-03-26T20:32:15Z</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000020_reviews_first-test-2026-ford-mustang-rtr-spec-5.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000020_features_best-used-3-row-suvs.md</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -858,21 +1130,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/stone-cold-steve-austin-desert-racing-kawasaki-teryx-h2</t>
+          <t>https://www.motortrend.com/features/best-used-hybrid-cars</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-26T19:35:30Z</t>
+          <t>2026-03-26T20:33:44Z</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000021_features_stone-cold-steve-austin-desert-racing-kawasaki-teryx-h2.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000021_features_best-used-hybrid-cars.md</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -880,21 +1166,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/sony-honda-mobility-afeela-evs-canceled</t>
+          <t>https://www.motortrend.com/features/most-reliable-suvs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-25T20:04:59Z</t>
+          <t>2026-03-25T19:51:42Z</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000022_news_sony-honda-mobility-afeela-evs-canceled.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000022_features_most-reliable-suvs.md</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -902,21 +1202,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/first-look-2026-easter-jeep-safari-wrangler-gladiator-cherokee-grand-wagoneer</t>
+          <t>https://www.motortrend.com/features/most-reliable-luxury-suvs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-27T09:10:14Z</t>
+          <t>2026-03-26T00:14:18Z</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000023_news_first-look-2026-easter-jeep-safari-wrangler-gladiator-cherokee-grand-wagoneer.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000023_features_most-reliable-luxury-suvs.md</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -924,21 +1238,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/first-look-2027-infiniti-qx65</t>
+          <t>https://www.motortrend.com/gear-reviews/amazon-spring-sale-2026-best-automotive-deals</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-26T23:24:59Z</t>
+          <t>2026-03-26T18:35:30Z</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000024_news_first-look-2027-infiniti-qx65.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000024_gear-reviews_amazon-spring-sale-2026-best-automotive-deals.md</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -946,21 +1274,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/first-look-2027-chevrolet-corvette-stingray-c8</t>
+          <t>https://www.motortrend.com/reviews/yearlong-review-update-3-2025-acura-adx-engine-stop-start</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-27T09:10:11Z</t>
+          <t>2026-03-27T09:10:12Z</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000025_news_first-look-2027-chevrolet-corvette-stingray-c8.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000025_reviews_yearlong-review-update-3-2025-acura-adx-engine-stop-start.md</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -968,21 +1310,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>18</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/tisha-johnson-slate-auto-designer-womens-history-month-2026</t>
+          <t>https://www.motortrend.com/reviews/yearlong-review-update-6-2025-toyota-land-crusier-how-to-drive</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-27T12:10:32Z</t>
+          <t>2026-03-27T12:10:35Z</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000026_features_tisha-johnson-slate-auto-designer-womens-history-month-2026.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000026_reviews_yearlong-review-update-6-2025-toyota-land-crusier-how-to-drive.md</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -990,21 +1346,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/bmw-suv-bigger-than-x7</t>
+          <t>https://www.motortrend.com/news/us-spec-first-look-nissan-z-nismo-manual</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-27T13:56:33Z</t>
+          <t>2026-03-25T17:47:28Z</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000027_news_bmw-suv-bigger-than-x7.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000027_news_us-spec-first-look-nissan-z-nismo-manual.md</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1012,21 +1382,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/bmw-ev-sports-car-demand-z4-successor</t>
+          <t>https://www.motortrend.com/news/2027-chevrolet-corvette-grand-sport-preview</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-30T10:10:53Z</t>
+          <t>2026-03-26T18:04:53Z</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000028_news_bmw-ev-sports-car-demand-z4-successor.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000028_news_2027-chevrolet-corvette-grand-sport-preview.md</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1034,21 +1418,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/lincoln-simulates-tropical-vacation-inside-navigator-nautilus-suvs</t>
+          <t>https://www.motortrend.com/reviews/first-test-2025-ford-bronco-rtr-rovr</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-25T22:27:06Z</t>
+          <t>2026-03-25T15:40:12Z</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000029_news_lincoln-simulates-tropical-vacation-inside-navigator-nautilus-suvs.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000029_reviews_first-test-2025-ford-bronco-rtr-rovr.md</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1056,21 +1454,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/first-look-2027-chevrolet-corvette-grand-sport-x</t>
+          <t>https://www.motortrend.com/reviews/yearlong-review-update-2-2025-hyundai-santa-fe-hybrid-limited-awd-winter</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-27T09:10:12Z</t>
+          <t>2026-03-30T14:58:52Z</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000030_news_first-look-2027-chevrolet-corvette-grand-sport-x.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000030_reviews_yearlong-review-update-2-2025-hyundai-santa-fe-hybrid-limited-awd-winter.md</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1078,21 +1490,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/first-look-review-2026-ford-mustang-troy-lee-designs-signature-edition</t>
+          <t>https://www.motortrend.com/reviews/first-test-2026-ford-mustang-rtr-spec-5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-27T09:10:18Z</t>
+          <t>2026-03-27T09:10:15Z</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000031_news_first-look-review-2026-ford-mustang-troy-lee-designs-signature-edition.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000031_reviews_first-test-2026-ford-mustang-rtr-spec-5.md</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1100,21 +1526,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>15</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/ev-charging-still-sucks-this-guy-is-making-it-better</t>
+          <t>https://www.motortrend.com/features/stone-cold-steve-austin-desert-racing-kawasaki-teryx-h2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-03-27T14:10:34Z</t>
+          <t>2026-03-26T19:35:30Z</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000032_news_ev-charging-still-sucks-this-guy-is-making-it-better.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000032_features_stone-cold-steve-austin-desert-racing-kawasaki-teryx-h2.md</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1122,21 +1562,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E32" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/first-drive-2026-porsche-cayenne-electric</t>
+          <t>https://www.motortrend.com/news/sony-honda-mobility-afeela-evs-canceled</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-03-27T13:10:32Z</t>
+          <t>2026-03-25T20:04:59Z</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000033_reviews_first-drive-2026-porsche-cayenne-electric.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000033_news_sony-honda-mobility-afeela-evs-canceled.md</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1144,21 +1598,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E33" t="n">
+        <v>18</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/first-look-review-2026-lotus-emira-scura</t>
+          <t>https://www.motortrend.com/news/first-look-2026-easter-jeep-safari-wrangler-gladiator-cherokee-grand-wagoneer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-03-26T21:55:40Z</t>
+          <t>2026-03-27T09:10:14Z</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000034_news_first-look-review-2026-lotus-emira-scura.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000034_news_first-look-2026-easter-jeep-safari-wrangler-gladiator-cherokee-grand-wagoneer.md</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1166,21 +1634,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/first-test-2026-volvo-xc60-t8</t>
+          <t>https://www.motortrend.com/news/first-look-2027-infiniti-qx65</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-30T11:10:18Z</t>
+          <t>2026-03-26T23:24:59Z</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000035_reviews_first-test-2026-volvo-xc60-t8.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000035_news_first-look-2027-infiniti-qx65.md</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1188,21 +1670,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E35" t="n">
+        <v>18</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/first-test-2026-toyota-c-hr-dual-motor-awd</t>
+          <t>https://www.motortrend.com/news/first-look-2027-chevrolet-corvette-stingray-c8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-30T13:10:34Z</t>
+          <t>2026-03-27T09:10:11Z</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000036_reviews_first-test-2026-toyota-c-hr-dual-motor-awd.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000036_news_first-look-2027-chevrolet-corvette-stingray-c8.md</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1210,21 +1706,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E36" t="n">
+        <v>25</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/acura-40th-anniversary-da-integra-race-car-build</t>
+          <t>https://www.motortrend.com/features/tisha-johnson-slate-auto-designer-womens-history-month-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-27T15:17:59Z</t>
+          <t>2026-03-27T12:10:32Z</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000037_news_acura-40th-anniversary-da-integra-race-car-build.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000037_features_tisha-johnson-slate-auto-designer-womens-history-month-2026.md</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1232,21 +1742,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/2027-slate-auto-truck-pricing-delivery-announcements</t>
+          <t>https://www.motortrend.com/news/bmw-suv-bigger-than-x7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-27T15:35:20Z</t>
+          <t>2026-03-27T13:56:33Z</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000038_news_2027-slate-auto-truck-pricing-delivery-announcements.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000038_news_bmw-suv-bigger-than-x7.md</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1254,21 +1778,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/first-look-2026-ram-1500-america-250-editions</t>
+          <t>https://www.motortrend.com/news/bmw-ev-sports-car-demand-z4-successor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-27T17:10:12Z</t>
+          <t>2026-03-30T10:10:53Z</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000039_news_first-look-2026-ram-1500-america-250-editions.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000039_news_bmw-ev-sports-car-demand-z4-successor.md</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1276,21 +1814,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/chevrolet/corvette-2027</t>
+          <t>https://www.motortrend.com/news/lincoln-simulates-tropical-vacation-inside-navigator-nautilus-suvs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-27T18:21:45Z</t>
+          <t>2026-03-25T22:27:06Z</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000040_cars_chevrolet_corvette-2027.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000040_news_lincoln-simulates-tropical-vacation-inside-navigator-nautilus-suvs.md</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1298,21 +1850,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E40" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/news/tesla-minivan-rumor-coming-soon-maybe-something-cooler-musk-says</t>
+          <t>https://www.motortrend.com/news/first-look-2027-chevrolet-corvette-grand-sport-x</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-27T22:39:16Z</t>
+          <t>2026-03-27T09:10:12Z</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000041_news_tesla-minivan-rumor-coming-soon-maybe-something-cooler-musk-says.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000041_news_first-look-2027-chevrolet-corvette-grand-sport-x.md</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1320,21 +1886,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E41" t="n">
+        <v>22</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/first-test-2026-nissan-pathfinder-platinum</t>
+          <t>https://www.motortrend.com/news/first-look-review-2026-ford-mustang-troy-lee-designs-signature-edition</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-30T14:10:32Z</t>
+          <t>2026-03-27T09:10:18Z</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000042_reviews_first-test-2026-nissan-pathfinder-platinum.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000042_news_first-look-review-2026-ford-mustang-troy-lee-designs-signature-edition.md</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1342,21 +1922,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/reviews/first-drive-2026-aston-martin-valhalla</t>
+          <t>https://www.motortrend.com/news/ev-charging-still-sucks-this-guy-is-making-it-better</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-30T10:08:08Z</t>
+          <t>2026-03-27T14:10:34Z</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000043_reviews_first-drive-2026-aston-martin-valhalla.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000043_news_ev-charging-still-sucks-this-guy-is-making-it-better.md</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1364,21 +1958,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E43" t="n">
+        <v>22</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/subaru/forester/2025</t>
+          <t>https://www.motortrend.com/reviews/first-drive-2026-porsche-cayenne-electric</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-25T15:17:10Z</t>
+          <t>2026-03-27T13:10:32Z</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000044_cars_subaru_forester_2025.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000044_reviews_first-drive-2026-porsche-cayenne-electric.md</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1386,21 +1994,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E44" t="n">
+        <v>55</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/mercedes-benz/gt-coupe/2026</t>
+          <t>https://www.motortrend.com/news/first-look-review-2026-lotus-emira-scura</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-27T19:55:52Z</t>
+          <t>2026-03-26T21:55:40Z</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000045_cars_mercedes-benz_gt-coupe_2026.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000045_news_first-look-review-2026-lotus-emira-scura.md</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1408,21 +2030,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/mercedes-benz/sl-class/2026</t>
+          <t>https://www.motortrend.com/reviews/first-test-2026-volvo-xc60-t8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-27T19:53:30Z</t>
+          <t>2026-03-30T11:10:18Z</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000046_cars_mercedes-benz_sl-class_2026.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000046_reviews_first-test-2026-volvo-xc60-t8.md</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1430,21 +2066,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E46" t="n">
+        <v>18</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/mercedes-benz/gt-4-door/2026</t>
+          <t>https://www.motortrend.com/reviews/first-test-2026-toyota-c-hr-dual-motor-awd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-27T19:58:02Z</t>
+          <t>2026-03-30T13:10:34Z</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000047_cars_mercedes-benz_gt-4-door_2026.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000047_reviews_first-test-2026-toyota-c-hr-dual-motor-awd.md</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1452,21 +2102,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/chevrolet/silverado/2027</t>
+          <t>https://www.motortrend.com/news/acura-40th-anniversary-da-integra-race-car-build</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-26T20:21:20Z</t>
+          <t>2026-03-27T15:17:59Z</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000048_cars_chevrolet_silverado_2027.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000048_news_acura-40th-anniversary-da-integra-race-car-build.md</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1474,21 +2138,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E48" t="n">
+        <v>18</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/infiniti/qx65/2027</t>
+          <t>https://www.motortrend.com/news/2027-slate-auto-truck-pricing-delivery-announcements</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-26T23:15:10Z</t>
+          <t>2026-03-27T15:35:20Z</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000049_cars_infiniti_qx65_2027.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000049_news_2027-slate-auto-truck-pricing-delivery-announcements.md</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1496,21 +2174,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/cars/mercedes-benz/2027-mercedes-benz-s-class</t>
+          <t>https://www.motortrend.com/news/first-look-2026-ram-1500-america-250-editions</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-25T17:22:46Z</t>
+          <t>2026-03-27T17:10:12Z</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000050_cars_mercedes-benz_2027-mercedes-benz-s-class.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000050_news_first-look-2026-ram-1500-america-250-editions.md</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1518,21 +2210,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E50" t="n">
+        <v>8</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.motortrend.com/features/bestselling-cars-in-each-state</t>
+          <t>https://www.motortrend.com/cars/chevrolet/corvette-2027</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-26T20:29:38Z</t>
+          <t>2026-03-27T18:21:45Z</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.motortrend.com/row_000051_features_bestselling-cars-in-each-state.md</t>
+          <t>scraped_markdown/www.motortrend.com/row_000051_cars_chevrolet_corvette-2027.md</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1540,28 +2246,488 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E51" t="n">
+        <v>15</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>https://www.motortrend.com/news/tesla-minivan-rumor-coming-soon-maybe-something-cooler-musk-says</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-03-27T22:39:16Z</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000052_news_tesla-minivan-rumor-coming-soon-maybe-something-cooler-musk-says.md</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>8</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/reviews/first-test-2026-nissan-pathfinder-platinum</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-03-30T14:10:32Z</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000053_reviews_first-test-2026-nissan-pathfinder-platinum.md</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/reviews/first-drive-2026-aston-martin-valhalla</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-03-30T22:12:25Z</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000054_reviews_first-drive-2026-aston-martin-valhalla.md</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>35</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/sponsored/as-adas-becomes-ubiquitous-the-auto-industry-seeks-safer-smoother-journeysacross-city-streets-highways-and-rural-roads</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-03-30T19:58:20Z</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000055_sponsored_as-adas-becomes-ubiquitous-the-auto-industry-seeks-safer-smoother-journeysacross-city-streets-highways-and-rur.md</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>52</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/cars/subaru/forester/2025</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-03-25T15:17:10Z</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000056_cars_subaru_forester_2025.md</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>25</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/cars/mercedes-benz/gt-coupe/2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-03-27T19:55:52Z</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000057_cars_mercedes-benz_gt-coupe_2026.md</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/cars/mercedes-benz/sl-class/2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-03-27T19:53:30Z</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000058_cars_mercedes-benz_sl-class_2026.md</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>12</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/cars/mercedes-benz/gt-4-door/2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-03-27T19:58:02Z</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000059_cars_mercedes-benz_gt-4-door_2026.md</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/cars/chevrolet/silverado/2027</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-03-26T20:21:20Z</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000060_cars_chevrolet_silverado_2027.md</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/cars/infiniti/qx65/2027</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-03-26T23:15:10Z</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000061_cars_infiniti_qx65_2027.md</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>15</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/cars/mercedes-benz/2027-mercedes-benz-s-class</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-03-25T17:22:46Z</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000062_cars_mercedes-benz_2027-mercedes-benz-s-class.md</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>25</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.motortrend.com/features/bestselling-cars-in-each-state</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-03-26T20:29:38Z</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000063_features_bestselling-cars-in-each-state.md</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>https://www.motortrend.com/features/best-cars-for-road-trips</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>2026-03-26T20:47:25Z</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>scraped_markdown/www.motortrend.com/row_000052_features_best-cars-for-road-trips.md</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.motortrend.com/row_000064_features_best-cars-for-road-trips.md</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1574,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,21 +2764,41 @@
           <t>scrape_status</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>relevance_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>semantic_match</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>processed_markdown_saved</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>processed_markdown_path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/resource_center/drivecentric/engagement-first-platforms-faster-response-stronger-sales/</t>
+          <t>https://www.autonews.com/general-motors/an-gm-factory-zero-idled-again-0330/</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-30T15:19:00.605Z</t>
+          <t>2026-03-30T21:07:02.543Z</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000002_resource_center_drivecentric_engagement-first-platforms-faster-response-stronger-sales.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000002_general-motors_an-gm-factory-zero-idled-again-0330.md</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1620,21 +2806,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/europe/ane-volvo-lynk-shared-sales-03030/</t>
+          <t>https://www.autonews.com/bmw/mini/an-mini-brand-quality-leaves-land-rover-in-the-dust-0330/</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-30T15:06:35.389Z</t>
+          <t>2026-03-31T00:43:54.139Z</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000003_europe_ane-volvo-lynk-shared-sales-03030.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000003_bmw_mini_an-mini-brand-quality-leaves-land-rover-in-the-dust-0330.md</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1642,21 +2842,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/ev/ane-ev-iran-charging-infrastructure-ford-0330/</t>
+          <t>https://www.autonews.com/car-concepts/an-2027-chevy-bolt-reviews-critics-corner-0330/</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-30T13:57:08.988Z</t>
+          <t>2026-03-30T19:59:50.111Z</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000004_ev_ane-ev-iran-charging-infrastructure-ford-0330.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000004_car-concepts_an-2027-chevy-bolt-reviews-critics-corner-0330.md</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1664,21 +2878,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>35</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/digital-edition/automotive-news/an-digital-edition-3-30-2026/</t>
+          <t>https://www.autonews.com/newsletters/daily-5/an-daily-5-gm-onstar-super-cruise-subscriptions-0330/</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-30T12:18:10.162Z</t>
+          <t>2026-03-30T20:17:24.803Z</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000005_digital-edition_automotive-news_an-digital-edition-3-30-2026.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000005_newsletters_daily-5_an-daily-5-gm-onstar-super-cruise-subscriptions-0330.md</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1686,21 +2914,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/china/an-how-china-brand-dealers-fare-in-mexico-europe-0330/</t>
+          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-dry-brakes-audi-ford-farley-0330/</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-30T13:45:19.371Z</t>
+          <t>2026-03-30T17:37:58.232Z</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000006_china_an-how-china-brand-dealers-fare-in-mexico-europe-0330.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000006_podcasts_daily-drive_an-daily-drive-dry-brakes-audi-ford-farley-0330.md</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1708,21 +2950,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>45</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/volkswagen/audi/ane-audi-five-cylinder-axed-to-meet-eu-rules-0330/</t>
+          <t>https://www.autonews.com/retail/an-truecar-dealership-rule-changes-0330/</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-30T13:44:28.097Z</t>
+          <t>2026-03-30T17:20:33.433Z</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000007_volkswagen_audi_ane-audi-five-cylinder-axed-to-meet-eu-rules-0330.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000007_retail_an-truecar-dealership-rule-changes-0330.md</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1730,21 +2986,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/general-motors/an-gm-digital-services-revenue-0330/</t>
+          <t>https://www.autonews.com/manufacturing/suppliers/an-stellantis-zf-chassis-supplier-lawsuit-0327/</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-30T10:00:04.434Z</t>
+          <t>2026-03-30T17:51:59.875Z</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000008_general-motors_an-gm-digital-services-revenue-0330.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000008_manufacturing_suppliers_an-stellantis-zf-chassis-supplier-lawsuit-0327.md</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1752,21 +3022,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/manufacturing/automakers/ane-mideast-war-hits-ferrari-bentley-0330/</t>
+          <t>https://www.autonews.com/resource_center/drivecentric/engagement-first-platforms-faster-response-stronger-sales/</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-30T10:26:38.2Z</t>
+          <t>2026-03-30T15:19:00.605Z</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000009_manufacturing_automakers_ane-mideast-war-hits-ferrari-bentley-0330.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000009_resource_center_drivecentric_engagement-first-platforms-faster-response-stronger-sales.md</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1774,21 +3058,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/geely/ane-geely-combined-engineering-hubs-germany-sweden-0329/</t>
+          <t>https://www.autonews.com/europe/ane-volvo-lynk-shared-sales-03030/</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-30T15:07:45.545Z</t>
+          <t>2026-03-30T15:06:35.389Z</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000010_geely_ane-geely-combined-engineering-hubs-germany-sweden-0329.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000010_europe_ane-volvo-lynk-shared-sales-03030.md</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1796,21 +3094,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/volkswagen/ane-skoda-ice-ev-strategy-working-europe-0329/</t>
+          <t>https://www.autonews.com/ev/ane-ev-iran-charging-infrastructure-ford-0330/</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-30T13:55:34.469Z</t>
+          <t>2026-03-30T19:59:01.583Z</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000011_volkswagen_ane-skoda-ice-ev-strategy-working-europe-0329.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000011_ev_ane-ev-iran-charging-infrastructure-ford-0330.md</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1818,21 +3130,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/technology/mobility/ane-robotaxis-tesla-mercedes-waymo-uber-0329/</t>
+          <t>https://www.autonews.com/digital-edition/automotive-news/an-digital-edition-3-30-2026/</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-30T14:32:34.655Z</t>
+          <t>2026-03-30T12:18:10.162Z</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000012_technology_mobility_ane-robotaxis-tesla-mercedes-waymo-uber-0329.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000012_digital-edition_automotive-news_an-digital-edition-3-30-2026.md</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1840,21 +3166,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/an-intersection-0329/</t>
+          <t>https://www.autonews.com/china/an-how-china-brand-dealers-fare-in-mexico-europe-0330/</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-29T11:00:01.775Z</t>
+          <t>2026-03-30T22:09:36.106Z</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000013_retail_an-intersection-0329.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000013_china_an-how-china-brand-dealers-fare-in-mexico-europe-0330.md</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1862,21 +3202,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/podcasts/shift/an-shift-podcast-dennis-fritsch-0329/</t>
+          <t>https://www.autonews.com/volkswagen/audi/ane-audi-five-cylinder-axed-to-meet-eu-rules-0330/</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-29T10:00:02.727Z</t>
+          <t>2026-03-30T16:40:38.682Z</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000014_podcasts_shift_an-shift-podcast-dennis-fritsch-0329.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000014_volkswagen_audi_ane-audi-five-cylinder-axed-to-meet-eu-rules-0330.md</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1884,21 +3238,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/used-cars/an-used-ev-auction-captive-strategy-0330/</t>
+          <t>https://www.autonews.com/general-motors/an-gm-digital-services-revenue-0330/</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-30T11:08:56.585Z</t>
+          <t>2026-03-30T18:23:56.082Z</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000015_retail_used-cars_an-used-ev-auction-captive-strategy-0330.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000015_general-motors_an-gm-digital-services-revenue-0330.md</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1906,21 +3274,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-wd-afeela-farley-stellantis/</t>
+          <t>https://www.autonews.com/manufacturing/automakers/ane-mideast-war-hits-ferrari-bentley-0330/</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-28T13:00:05.348Z</t>
+          <t>2026-03-30T20:04:23.648Z</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000016_podcasts_daily-drive_an-daily-drive-wd-afeela-farley-stellantis.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000016_manufacturing_automakers_ane-mideast-war-hits-ferrari-bentley-0330.md</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1928,21 +3310,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/classified/automotive-news-classifieds/</t>
+          <t>https://www.autonews.com/geely/ane-geely-combined-engineering-hubs-germany-sweden-0329/</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-27T20:52:45.411Z</t>
+          <t>2026-03-30T15:07:45.545Z</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000017_classified_automotive-news-classifieds.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000017_geely_ane-geely-combined-engineering-hubs-germany-sweden-0329.md</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1950,21 +3346,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/newsletters/daily-5/an-daily-5-an-new-york-auto-show-coverage-preview-0327/</t>
+          <t>https://www.autonews.com/volkswagen/ane-skoda-ice-ev-strategy-working-europe-0329/</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-27T19:22:33.253Z</t>
+          <t>2026-03-30T13:55:34.469Z</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000018_newsletters_daily-5_an-daily-5-an-new-york-auto-show-coverage-preview-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000018_volkswagen_ane-skoda-ice-ev-strategy-working-europe-0329.md</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1972,21 +3382,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-hyundai-production-wrenchway-gm-evs-0327/</t>
+          <t>https://www.autonews.com/technology/mobility/ane-robotaxis-tesla-mercedes-waymo-uber-0329/</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-27T18:41:10.535Z</t>
+          <t>2026-03-30T14:32:34.655Z</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000019_podcasts_daily-drive_an-daily-drive-hyundai-production-wrenchway-gm-evs-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000019_technology_mobility_ane-robotaxis-tesla-mercedes-waymo-uber-0329.md</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1994,21 +3418,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/manufacturing/anc-canadian-auto-news-week-march-23-2026/</t>
+          <t>https://www.autonews.com/retail/an-intersection-0329/</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-27T18:33:49.298Z</t>
+          <t>2026-03-29T11:00:01.775Z</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000020_manufacturing_anc-canadian-auto-news-week-march-23-2026.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000020_retail_an-intersection-0329.md</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2016,43 +3454,75 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/data-center/manufacturing-data/production-downtime/an-north-america-assembly-plant-downtime-033026/</t>
+          <t>https://www.autonews.com/podcasts/shift/an-shift-podcast-dennis-fritsch-0329/</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-27T17:24:53.763Z</t>
+          <t>2026-03-29T10:00:02.727Z</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000021_data-center_manufacturing-data_production-downtime_an-north-america-assembly-plant-downtime-033026.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000021_podcasts_shift_an-shift-podcast-dennis-fritsch-0329.md</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>success</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>72</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_autonews_com_sitemap/www.autonews.com/row_000021_podcasts_shift_an-shift-podcast-dennis-fritsch-0329_processed.md</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/sponsored/webinars/strategies-navigating-dram-chip-shortage/</t>
+          <t>https://www.autonews.com/retail/used-cars/an-used-ev-auction-captive-strategy-0330/</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-27T16:48:15.74Z</t>
+          <t>2026-03-30T11:08:56.585Z</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000022_sponsored_webinars_strategies-navigating-dram-chip-shortage.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000022_retail_used-cars_an-used-ev-auction-captive-strategy-0330.md</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2060,21 +3530,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/resource_center/sp-global/strategies-navigating-dram-chip-shortage-042226/</t>
+          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-wd-afeela-farley-stellantis/</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-27T17:06:24.02Z</t>
+          <t>2026-03-28T13:00:05.348Z</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000023_resource_center_sp-global_strategies-navigating-dram-chip-shortage-042226.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000023_podcasts_daily-drive_an-daily-drive-wd-afeela-farley-stellantis.md</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2082,21 +3566,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/service-and-parts/an-collision-repair-outside-support-0327/</t>
+          <t>https://www.autonews.com/classified/automotive-news-classifieds/</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-27T16:00:03.064Z</t>
+          <t>2026-03-27T20:52:45.411Z</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000024_retail_service-and-parts_an-collision-repair-outside-support-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000024_classified_automotive-news-classifieds.md</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2104,21 +3602,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/opinion/cartoons/an-leo-michael-cartoon-vehicle-affordability-0327/</t>
+          <t>https://www.autonews.com/newsletters/daily-5/an-daily-5-an-new-york-auto-show-coverage-preview-0327/</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-27T15:51:03.293Z</t>
+          <t>2026-03-27T19:22:33.253Z</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000025_opinion_cartoons_an-leo-michael-cartoon-vehicle-affordability-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000025_newsletters_daily-5_an-daily-5-an-new-york-auto-show-coverage-preview-0327.md</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2126,21 +3638,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/manufacturing/automakers/an-top-stories-porsche-audi-forge-ties-0327/</t>
+          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-hyundai-production-wrenchway-gm-evs-0327/</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-27T15:11:41.93Z</t>
+          <t>2026-03-27T18:41:10.535Z</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000026_manufacturing_automakers_an-top-stories-porsche-audi-forge-ties-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000026_podcasts_daily-drive_an-daily-drive-hyundai-production-wrenchway-gm-evs-0327.md</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2148,21 +3674,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/ford/an-ford-ceo-jim-farley-compensation-rises-0327/</t>
+          <t>https://www.autonews.com/manufacturing/anc-canadian-auto-news-week-march-23-2026/</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-27T19:17:27.048Z</t>
+          <t>2026-03-27T18:33:49.298Z</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000027_ford_an-ford-ceo-jim-farley-compensation-rises-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000027_manufacturing_anc-canadian-auto-news-week-march-23-2026.md</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2170,21 +3710,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/car-concepts/an-new-york-auto-show-preview-0327/</t>
+          <t>https://www.autonews.com/data-center/manufacturing-data/production-downtime/an-north-america-assembly-plant-downtime-033026/</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-29T13:39:01.817Z</t>
+          <t>2026-03-27T17:24:53.763Z</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000028_car-concepts_an-new-york-auto-show-preview-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000028_data-center_manufacturing-data_production-downtime_an-north-america-assembly-plant-downtime-033026.md</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2192,21 +3746,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/canada/anc-linamar-buys-winning-blw-germany-plants/</t>
+          <t>https://www.autonews.com/sponsored/webinars/strategies-navigating-dram-chip-shortage/</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-27T14:17:30.033Z</t>
+          <t>2026-03-27T16:48:15.74Z</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000029_canada_anc-linamar-buys-winning-blw-germany-plants.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000029_sponsored_webinars_strategies-navigating-dram-chip-shortage.md</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2214,21 +3782,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/ev/anc-china-evs-canada-cost-discount-0326/</t>
+          <t>https://www.autonews.com/resource_center/sp-global/strategies-navigating-dram-chip-shortage-042226/</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-27T20:19:17.915Z</t>
+          <t>2026-03-27T17:06:24.02Z</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000030_ev_anc-china-evs-canada-cost-discount-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000030_resource_center_sp-global_strategies-navigating-dram-chip-shortage-042226.md</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2236,21 +3818,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/anc-genesis-regina-dilawri-0327/</t>
+          <t>https://www.autonews.com/retail/service-and-parts/an-collision-repair-outside-support-0327/</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-27T16:59:47.48Z</t>
+          <t>2026-03-27T16:00:03.064Z</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000031_retail_anc-genesis-regina-dilawri-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000031_retail_service-and-parts_an-collision-repair-outside-support-0327.md</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2258,21 +3854,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/mergers-acquisitions/an-dealership-buy-sell-database-updates-0327/</t>
+          <t>https://www.autonews.com/opinion/cartoons/an-leo-michael-cartoon-vehicle-affordability-0327/</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-03-27T11:00:06.082Z</t>
+          <t>2026-03-27T15:51:03.293Z</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000032_retail_mergers-acquisitions_an-dealership-buy-sell-database-updates-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000032_opinion_cartoons_an-leo-michael-cartoon-vehicle-affordability-0327.md</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2280,21 +3890,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/volkswagen/ane-vw-rivian-partnership-winter-testing-0327/</t>
+          <t>https://www.autonews.com/manufacturing/automakers/an-top-stories-porsche-audi-forge-ties-0327/</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-03-27T11:13:31.122Z</t>
+          <t>2026-03-27T15:11:41.93Z</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000033_volkswagen_ane-vw-rivian-partnership-winter-testing-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000033_manufacturing_automakers_an-top-stories-porsche-audi-forge-ties-0327.md</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2302,21 +3926,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/ford/ane-ford-launches-cheap-china-built-ev-van-0327/</t>
+          <t>https://www.autonews.com/ford/an-ford-ceo-jim-farley-compensation-rises-0327/</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-03-27T15:37:16.076Z</t>
+          <t>2026-03-27T19:17:27.048Z</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000034_ford_ane-ford-launches-cheap-china-built-ev-van-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000034_ford_an-ford-ceo-jim-farley-compensation-rises-0327.md</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2324,21 +3962,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/service-and-parts/an-gm-service-learning-center-0327/</t>
+          <t>https://www.autonews.com/car-concepts/an-new-york-auto-show-preview-0327/</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-27T10:00:10.406Z</t>
+          <t>2026-03-29T13:39:01.817Z</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000035_retail_service-and-parts_an-gm-service-learning-center-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000035_car-concepts_an-new-york-auto-show-preview-0327.md</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2346,21 +3998,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E35" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/an-ftc-letters-dealer-vehicle-availability-0327/</t>
+          <t>https://www.autonews.com/canada/anc-linamar-buys-winning-blw-germany-plants/</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-27T19:18:33.83Z</t>
+          <t>2026-03-27T14:17:30.033Z</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000036_retail_an-ftc-letters-dealer-vehicle-availability-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000036_canada_anc-linamar-buys-winning-blw-germany-plants.md</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2368,21 +4034,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/stellantis/ferrari/ane-ferrari-middle-east-shipment-restarted-0327/</t>
+          <t>https://www.autonews.com/ev/anc-china-evs-canada-cost-discount-0326/</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-27T09:32:26.12Z</t>
+          <t>2026-03-27T20:19:17.915Z</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000037_stellantis_ferrari_ane-ferrari-middle-east-shipment-restarted-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000037_ev_anc-china-evs-canada-cost-discount-0326.md</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2390,21 +4070,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/jaguar-land-rover/ane-jlr-production-halt-uk-supplier-issue-0327/</t>
+          <t>https://www.autonews.com/retail/anc-genesis-regina-dilawri-0327/</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-27T09:48:39.683Z</t>
+          <t>2026-03-27T16:59:47.48Z</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000038_jaguar-land-rover_ane-jlr-production-halt-uk-supplier-issue-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000038_retail_anc-genesis-regina-dilawri-0327.md</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2412,21 +4106,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/sales/ane-germany-automakers-tariff-free-australia-trade-eu-0327/</t>
+          <t>https://www.autonews.com/retail/mergers-acquisitions/an-dealership-buy-sell-database-updates-0327/</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-27T14:59:30.753Z</t>
+          <t>2026-03-27T11:00:06.082Z</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000039_retail_sales_ane-germany-automakers-tariff-free-australia-trade-eu-0327.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000039_retail_mergers-acquisitions_an-dealership-buy-sell-database-updates-0327.md</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2434,43 +4142,75 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/podcasts/canada-conversations/anc-automotive-news-canada-podcast-march-27/</t>
+          <t>https://www.autonews.com/volkswagen/ane-vw-rivian-partnership-winter-testing-0327/</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-27T02:07:19.898Z</t>
+          <t>2026-03-27T11:13:31.122Z</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000040_podcasts_canada-conversations_anc-automotive-news-canada-podcast-march-27.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000040_volkswagen_ane-vw-rivian-partnership-winter-testing-0327.md</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>success</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>65</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_autonews_com_sitemap/www.autonews.com/row_000040_volkswagen_ane-vw-rivian-partnership-winter-testing-0327_processed.md</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/nissan/an-infiniti-launches-qx65-0326/</t>
+          <t>https://www.autonews.com/ford/ane-ford-launches-cheap-china-built-ev-van-0327/</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-26T23:00:03.522Z</t>
+          <t>2026-03-27T15:37:16.076Z</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000041_nissan_an-infiniti-launches-qx65-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000041_ford_ane-ford-launches-cheap-china-built-ev-van-0327.md</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2478,21 +4218,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/hyundai/an-hyundai-north-america-expansion-0326/</t>
+          <t>https://www.autonews.com/retail/service-and-parts/an-gm-service-learning-center-0327/</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-27T14:18:39.846Z</t>
+          <t>2026-03-27T10:00:10.406Z</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000042_hyundai_an-hyundai-north-america-expansion-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000042_retail_service-and-parts_an-gm-service-learning-center-0327.md</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2500,21 +4254,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/classified/people_on_the_move/an-potm-mike-mcgroarty-dan-egan/</t>
+          <t>https://www.autonews.com/retail/an-ftc-letters-dealer-vehicle-availability-0327/</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-26T19:32:57.861Z</t>
+          <t>2026-03-27T19:18:33.83Z</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000043_classified_people_on_the_move_an-potm-mike-mcgroarty-dan-egan.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000043_retail_an-ftc-letters-dealer-vehicle-availability-0327.md</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2522,21 +4290,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/an-iowa-dealership-stellantis-ford-out-of-trust-0326/</t>
+          <t>https://www.autonews.com/stellantis/ferrari/ane-ferrari-middle-east-shipment-restarted-0327/</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-26T19:37:44.459Z</t>
+          <t>2026-03-27T09:32:26.12Z</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000044_retail_an-iowa-dealership-stellantis-ford-out-of-trust-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000044_stellantis_ferrari_ane-ferrari-middle-east-shipment-restarted-0327.md</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2544,21 +4326,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/newsletters/daily-5/an-daily-5-iowa-dealership-bankruptcy-0326/</t>
+          <t>https://www.autonews.com/jaguar-land-rover/ane-jlr-production-halt-uk-supplier-issue-0327/</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-26T19:56:21.69Z</t>
+          <t>2026-03-27T09:48:39.683Z</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000045_newsletters_daily-5_an-daily-5-iowa-dealership-bankruptcy-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000045_jaguar-land-rover_ane-jlr-production-halt-uk-supplier-issue-0327.md</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2566,21 +4362,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-afeela-cancellations-q1-sales-preview/</t>
+          <t>https://www.autonews.com/retail/sales/ane-germany-automakers-tariff-free-australia-trade-eu-0327/</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-26T18:55:23.558Z</t>
+          <t>2026-03-27T14:59:30.753Z</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000046_podcasts_daily-drive_an-daily-drive-afeela-cancellations-q1-sales-preview.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000046_retail_sales_ane-germany-automakers-tariff-free-australia-trade-eu-0327.md</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2588,21 +4398,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/car-concepts/an-chevy-corvette-grand-sport-new-engine-0326/</t>
+          <t>https://www.autonews.com/podcasts/canada-conversations/anc-automotive-news-canada-podcast-march-27/</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-26T16:51:18.278Z</t>
+          <t>2026-03-27T02:07:19.898Z</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000047_car-concepts_an-chevy-corvette-grand-sport-new-engine-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000047_podcasts_canada-conversations_anc-automotive-news-canada-podcast-march-27.md</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2610,21 +4434,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/data-center/sales-data/incentives/an-u-s-customer-incentives-march-30-2026/</t>
+          <t>https://www.autonews.com/nissan/an-infiniti-launches-qx65-0326/</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-26T16:44:52.961Z</t>
+          <t>2026-03-26T23:00:03.522Z</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000048_data-center_sales-data_incentives_an-u-s-customer-incentives-march-30-2026.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000048_nissan_an-infiniti-launches-qx65-0326.md</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2632,21 +4470,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E48" t="n">
+        <v>10</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/mergers-acquisitions/an-sonic-automotive-sells-three-dealerships-0326/</t>
+          <t>https://www.autonews.com/hyundai/an-hyundai-north-america-expansion-0326/</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-30T14:32:41.91Z</t>
+          <t>2026-03-27T14:18:39.846Z</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000049_retail_mergers-acquisitions_an-sonic-automotive-sells-three-dealerships-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000049_hyundai_an-hyundai-north-america-expansion-0326.md</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2654,21 +4506,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E49" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/sales/an-q1-sales-preview-0326/</t>
+          <t>https://www.autonews.com/classified/people_on_the_move/an-potm-mike-mcgroarty-dan-egan/</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-27T15:53:38.589Z</t>
+          <t>2026-03-26T19:32:57.861Z</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000050_retail_sales_an-q1-sales-preview-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000050_classified_people_on_the_move_an-potm-mike-mcgroarty-dan-egan.md</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2676,21 +4542,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/resource_center/roland-berger/an-the-iran-conflict-global-supply-implications-beyond-oil/</t>
+          <t>https://www.autonews.com/retail/an-iowa-dealership-stellantis-ford-out-of-trust-0326/</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-26T15:36:52.554Z</t>
+          <t>2026-03-26T19:37:44.459Z</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000051_resource_center_roland-berger_an-the-iran-conflict-global-supply-implications-beyond-oil.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000051_retail_an-iowa-dealership-stellantis-ford-out-of-trust-0326.md</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2698,21 +4578,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/manufacturing/suppliers/ev-battery-makers-pivot-to-new-markets-0326/</t>
+          <t>https://www.autonews.com/newsletters/daily-5/an-daily-5-iowa-dealership-bankruptcy-0326/</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-26T19:42:19.735Z</t>
+          <t>2026-03-26T19:56:21.69Z</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000052_manufacturing_suppliers_ev-battery-makers-pivot-to-new-markets-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000052_newsletters_daily-5_an-daily-5-iowa-dealership-bankruptcy-0326.md</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2720,21 +4614,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/stellantis/an-easter-jeep-safari-0326/</t>
+          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-afeela-cancellations-q1-sales-preview/</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-26T13:13:29.067Z</t>
+          <t>2026-03-26T18:55:23.558Z</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000053_stellantis_an-easter-jeep-safari-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000053_podcasts_daily-drive_an-daily-drive-afeela-cancellations-q1-sales-preview.md</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2742,21 +4650,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E53" t="n">
+        <v>15</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/ev/anc-china-automakers-australia-canada-expansion-0326/</t>
+          <t>https://www.autonews.com/car-concepts/an-chevy-corvette-grand-sport-new-engine-0326/</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-27T01:10:35.691Z</t>
+          <t>2026-03-26T16:51:18.278Z</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000054_ev_anc-china-automakers-australia-canada-expansion-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000054_car-concepts_an-chevy-corvette-grand-sport-new-engine-0326.md</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2764,21 +4686,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E54" t="n">
+        <v>35</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/mercedes-benz/an-mercedes-amg-gt-racer-0326/</t>
+          <t>https://www.autonews.com/data-center/sales-data/incentives/an-u-s-customer-incentives-march-30-2026/</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-27T13:18:06.635Z</t>
+          <t>2026-03-26T16:44:52.961Z</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000055_mercedes-benz_an-mercedes-amg-gt-racer-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000055_data-center_sales-data_incentives_an-u-s-customer-incentives-march-30-2026.md</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2786,21 +4722,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/regulation-safety/an-iran-war-chaos-0326/</t>
+          <t>https://www.autonews.com/retail/mergers-acquisitions/an-sonic-automotive-sells-three-dealerships-0326/</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-26T14:30:35.394Z</t>
+          <t>2026-03-30T14:32:41.91Z</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000056_regulation-safety_an-iran-war-chaos-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000056_retail_mergers-acquisitions_an-sonic-automotive-sells-three-dealerships-0326.md</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2808,21 +4758,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/stellantis/an-stellantis-parking-tickets-rival-brands-0326/</t>
+          <t>https://www.autonews.com/retail/sales/an-q1-sales-preview-0326/</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-26T22:56:09.513Z</t>
+          <t>2026-03-27T15:53:38.589Z</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000057_stellantis_an-stellantis-parking-tickets-rival-brands-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000057_retail_sales_an-q1-sales-preview-0326.md</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2830,21 +4794,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/opinion/editorials/an-editorial-dealers-should-prepare-for-ai-0326/</t>
+          <t>https://www.autonews.com/resource_center/roland-berger/an-the-iran-conflict-global-supply-implications-beyond-oil/</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-26T11:48:09.259Z</t>
+          <t>2026-03-26T15:36:52.554Z</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000058_opinion_editorials_an-editorial-dealers-should-prepare-for-ai-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000058_resource_center_roland-berger_an-the-iran-conflict-global-supply-implications-beyond-oil.md</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2852,21 +4830,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E58" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/technology/mobility/ane-uber-ponyai-verne-croatia-robotaxi-europe-first-0326/</t>
+          <t>https://www.autonews.com/manufacturing/suppliers/ev-battery-makers-pivot-to-new-markets-0326/</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-26T10:20:04.378Z</t>
+          <t>2026-03-26T19:42:19.735Z</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000059_technology_mobility_ane-uber-ponyai-verne-croatia-robotaxi-europe-first-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000059_manufacturing_suppliers_ev-battery-makers-pivot-to-new-markets-0326.md</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2874,21 +4866,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/saic/mg/ane-mg-semisolid-state-mg4-europe-0326/</t>
+          <t>https://www.autonews.com/stellantis/an-easter-jeep-safari-0326/</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-26T14:19:49.637Z</t>
+          <t>2026-03-26T13:13:29.067Z</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000060_saic_mg_ane-mg-semisolid-state-mg4-europe-0326.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000060_stellantis_an-easter-jeep-safari-0326.md</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2896,21 +4902,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/newsletters/daily-5/an-daily-5-stellantis-turnaround-chrysler-0325/</t>
+          <t>https://www.autonews.com/ev/anc-china-automakers-australia-canada-expansion-0326/</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-25T19:51:37.012Z</t>
+          <t>2026-03-27T01:10:35.691Z</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000061_newsletters_daily-5_an-daily-5-stellantis-turnaround-chrysler-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000061_ev_anc-china-automakers-australia-canada-expansion-0326.md</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2918,21 +4938,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E61" t="n">
+        <v>10</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/service-and-parts/an-guest-commentary-joshi-0325/</t>
+          <t>https://www.autonews.com/mercedes-benz/an-mercedes-amg-gt-racer-0326/</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-26T12:01:15.458Z</t>
+          <t>2026-03-27T13:18:06.635Z</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000062_retail_service-and-parts_an-guest-commentary-joshi-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000062_mercedes-benz_an-mercedes-amg-gt-racer-0326.md</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2940,21 +4974,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E62" t="n">
+        <v>15</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-mark-templin-afeela/</t>
+          <t>https://www.autonews.com/regulation-safety/an-iran-war-chaos-0326/</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-03-25T17:44:13.356Z</t>
+          <t>2026-03-26T14:30:35.394Z</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000063_podcasts_daily-drive_an-daily-drive-mark-templin-afeela.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000063_regulation-safety_an-iran-war-chaos-0326.md</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2962,21 +5010,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/events/leading-women-conference/an-leading-women-conference-2026-0325/</t>
+          <t>https://www.autonews.com/stellantis/an-stellantis-parking-tickets-rival-brands-0326/</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-27T18:36:32.717Z</t>
+          <t>2026-03-26T22:56:09.513Z</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000064_events_leading-women-conference_an-leading-women-conference-2026-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000064_stellantis_an-stellantis-parking-tickets-rival-brands-0326.md</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2984,21 +5046,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/resource_center/Experian/rising-dealer-fraud-experian-threat-report/</t>
+          <t>https://www.autonews.com/opinion/editorials/an-editorial-dealers-should-prepare-for-ai-0326/</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-25T16:44:06.477Z</t>
+          <t>2026-03-26T11:48:09.259Z</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000065_resource_center_Experian_rising-dealer-fraud-experian-threat-report.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000065_opinion_editorials_an-editorial-dealers-should-prepare-for-ai-0326.md</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3006,21 +5082,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/opinion/letters/an-letter-conant-0325/</t>
+          <t>https://www.autonews.com/technology/mobility/ane-uber-ponyai-verne-croatia-robotaxi-europe-first-0326/</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-25T16:30:09.175Z</t>
+          <t>2026-03-26T10:20:04.378Z</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000066_opinion_letters_an-letter-conant-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000066_technology_mobility_ane-uber-ponyai-verne-croatia-robotaxi-europe-first-0326.md</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3028,43 +5118,75 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E66" t="n">
+        <v>55</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/finance-insurance/an-guest-commentary-steenbergh-0325/</t>
+          <t>https://www.autonews.com/saic/mg/ane-mg-semisolid-state-mg4-europe-0326/</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-26T13:25:17.541Z</t>
+          <t>2026-03-26T14:19:49.637Z</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000067_retail_finance-insurance_an-guest-commentary-steenbergh-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000067_saic_mg_ane-mg-semisolid-state-mg4-europe-0326.md</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>success</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>88</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_autonews_com_sitemap/www.autonews.com/row_000067_saic_mg_ane-mg-semisolid-state-mg4-europe-0326_processed.md</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/china/an-china-majority-car-dealerships-unprofitable-price-war-cada-0325/</t>
+          <t>https://www.autonews.com/newsletters/daily-5/an-daily-5-stellantis-turnaround-chrysler-0325/</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-26T11:32:24.867Z</t>
+          <t>2026-03-25T19:51:37.012Z</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000068_china_an-china-majority-car-dealerships-unprofitable-price-war-cada-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000068_newsletters_daily-5_an-daily-5-stellantis-turnaround-chrysler-0325.md</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3072,21 +5194,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/resource_center/urban-science/discover-clear-decisions-modern-network-planning/</t>
+          <t>https://www.autonews.com/retail/service-and-parts/an-guest-commentary-joshi-0325/</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-25T21:15:08.79Z</t>
+          <t>2026-03-26T12:01:15.458Z</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000069_resource_center_urban-science_discover-clear-decisions-modern-network-planning.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000069_retail_service-and-parts_an-guest-commentary-joshi-0325.md</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3094,21 +5230,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E69" t="n">
+        <v>12</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/car-concepts/an-ev-cancellations-delays-2026-0313/</t>
+          <t>https://www.autonews.com/podcasts/daily-drive/an-daily-drive-mark-templin-afeela/</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-25T15:40:31.71Z</t>
+          <t>2026-03-25T17:44:13.356Z</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000070_car-concepts_an-ev-cancellations-delays-2026-0313.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000070_podcasts_daily-drive_an-daily-drive-mark-templin-afeela.md</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3116,21 +5266,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/volkswagen/skoda/ane-skoda-exits-china-marker-0325/</t>
+          <t>https://www.autonews.com/events/leading-women-conference/an-leading-women-conference-2026-0325/</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-26T10:26:27.25Z</t>
+          <t>2026-03-27T18:36:32.717Z</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000071_volkswagen_skoda_ane-skoda-exits-china-marker-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000071_events_leading-women-conference_an-leading-women-conference-2026-0325.md</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3138,21 +5302,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/resource_center/urban-science/navigating-the-complexities-of-modern-network-planning/</t>
+          <t>https://www.autonews.com/resource_center/Experian/rising-dealer-fraud-experian-threat-report/</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-25T14:31:45.748Z</t>
+          <t>2026-03-25T16:44:06.477Z</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000072_resource_center_urban-science_navigating-the-complexities-of-modern-network-planning.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000072_resource_center_Experian_rising-dealer-fraud-experian-threat-report.md</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3160,21 +5338,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E72" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/toyota/an-toyota-suppliers-koji-sato-kenta-kon-warning-boost-productivity-0325/</t>
+          <t>https://www.autonews.com/opinion/letters/an-letter-conant-0325/</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-25T18:26:12.913Z</t>
+          <t>2026-03-25T16:30:09.175Z</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000073_toyota_an-toyota-suppliers-koji-sato-kenta-kon-warning-boost-productivity-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000073_opinion_letters_an-letter-conant-0325.md</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3182,21 +5374,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E73" t="n">
+        <v>5</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/stellantis/ane-leapmotor-new-models-europe-0325/</t>
+          <t>https://www.autonews.com/retail/finance-insurance/an-guest-commentary-steenbergh-0325/</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-27T01:13:01.393Z</t>
+          <t>2026-03-26T13:25:17.541Z</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000074_stellantis_ane-leapmotor-new-models-europe-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000074_retail_finance-insurance_an-guest-commentary-steenbergh-0325.md</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3204,21 +5410,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/jaguar-land-rover/ane-jlr-freelander-readied-chery-phev-0325/</t>
+          <t>https://www.autonews.com/china/an-china-majority-car-dealerships-unprofitable-price-war-cada-0325/</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-27T08:33:16.254Z</t>
+          <t>2026-03-26T11:32:24.867Z</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000075_jaguar-land-rover_ane-jlr-freelander-readied-chery-phev-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000075_china_an-china-majority-car-dealerships-unprofitable-price-war-cada-0325.md</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3226,21 +5446,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E75" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/anc-bc-emissions/</t>
+          <t>https://www.autonews.com/resource_center/urban-science/discover-clear-decisions-modern-network-planning/</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-27T12:07:47.335Z</t>
+          <t>2026-03-25T21:15:08.79Z</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000076_retail_anc-bc-emissions.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000076_resource_center_urban-science_discover-clear-decisions-modern-network-planning.md</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3248,21 +5482,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E76" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/retail/finance-insurance/an-ftc-letters-dealers-social-media-0325/</t>
+          <t>https://www.autonews.com/car-concepts/an-ev-cancellations-delays-2026-0313/</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-27T17:52:03.184Z</t>
+          <t>2026-03-25T15:40:31.71Z</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000077_retail_finance-insurance_an-ftc-letters-dealers-social-media-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000077_car-concepts_an-ev-cancellations-delays-2026-0313.md</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3270,21 +5518,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/honda/an-sony-honda-mobility-cancels-afeela-evs-north-america-0325/</t>
+          <t>https://www.autonews.com/volkswagen/skoda/ane-skoda-exits-china-marker-0325/</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-03-27T18:11:18.846Z</t>
+          <t>2026-03-26T10:26:27.25Z</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000078_honda_an-sony-honda-mobility-cancels-afeela-evs-north-america-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000078_volkswagen_skoda_ane-skoda-exits-china-marker-0325.md</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3292,21 +5554,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/stellantis/ane-stellantis-elkann-stronger-cost-cuts-improved-products-0325/</t>
+          <t>https://www.autonews.com/resource_center/urban-science/navigating-the-complexities-of-modern-network-planning/</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-26T11:34:04.75Z</t>
+          <t>2026-03-25T14:31:45.748Z</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000079_stellantis_ane-stellantis-elkann-stronger-cost-cuts-improved-products-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000079_resource_center_urban-science_navigating-the-complexities-of-modern-network-planning.md</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3314,21 +5590,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E79" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/stellantis/an-jeep-grand-wagoneer-campaign-0324/</t>
+          <t>https://www.autonews.com/toyota/an-toyota-suppliers-koji-sato-kenta-kon-warning-boost-productivity-0325/</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-25T13:29:42.451Z</t>
+          <t>2026-03-25T18:26:12.913Z</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000080_stellantis_an-jeep-grand-wagoneer-campaign-0324.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000080_toyota_an-toyota-suppliers-koji-sato-kenta-kon-warning-boost-productivity-0325.md</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3336,21 +5626,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E80" t="n">
+        <v>10</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/stellantis/an-stellantis-design-direction-0325/</t>
+          <t>https://www.autonews.com/stellantis/ane-leapmotor-new-models-europe-0325/</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-27T14:47:05.646Z</t>
+          <t>2026-03-27T01:13:01.393Z</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000081_stellantis_an-stellantis-design-direction-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000081_stellantis_ane-leapmotor-new-models-europe-0325.md</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3358,21 +5662,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E81" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.autonews.com/volkswagen/ane-vw-israeli-defense-jobs-germany-plant-0325/</t>
+          <t>https://www.autonews.com/jaguar-land-rover/ane-jlr-freelander-readied-chery-phev-0325/</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-25T14:55:57.62Z</t>
+          <t>2026-03-27T08:33:16.254Z</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.autonews.com/row_000082_volkswagen_ane-vw-israeli-defense-jobs-germany-plant-0325.md</t>
+          <t>scraped_markdown/www.autonews.com/row_000082_jaguar-land-rover_ane-jlr-freelander-readied-chery-phev-0325.md</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3380,28 +5698,308 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E82" t="n">
+        <v>25</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>https://www.autonews.com/retail/anc-bc-emissions/</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-03-27T12:07:47.335Z</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000083_retail_anc-bc-emissions.md</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.autonews.com/retail/finance-insurance/an-ftc-letters-dealers-social-media-0325/</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-03-27T17:52:03.184Z</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000084_retail_finance-insurance_an-ftc-letters-dealers-social-media-0325.md</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.autonews.com/honda/an-sony-honda-mobility-cancels-afeela-evs-north-america-0325/</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-03-27T18:11:18.846Z</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000085_honda_an-sony-honda-mobility-cancels-afeela-evs-north-america-0325.md</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.autonews.com/stellantis/ane-stellantis-elkann-stronger-cost-cuts-improved-products-0325/</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-03-26T11:34:04.75Z</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000086_stellantis_ane-stellantis-elkann-stronger-cost-cuts-improved-products-0325.md</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.autonews.com/stellantis/an-jeep-grand-wagoneer-campaign-0324/</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-03-25T13:29:42.451Z</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000087_stellantis_an-jeep-grand-wagoneer-campaign-0324.md</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.autonews.com/stellantis/an-stellantis-design-direction-0325/</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-03-27T14:47:05.646Z</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000088_stellantis_an-stellantis-design-direction-0325.md</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.autonews.com/volkswagen/ane-vw-israeli-defense-jobs-germany-plant-0325/</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-03-25T14:55:57.62Z</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000089_volkswagen_ane-vw-israeli-defense-jobs-germany-plant-0325.md</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>https://www.autonews.com/byd/ane-byd-gods-eye-safety-self-driving-flaws-0325/</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>2026-03-25T11:11:46.792Z</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>scraped_markdown/www.autonews.com/row_000083_byd_ane-byd-gods-eye-safety-self-driving-flaws-0325.md</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.autonews.com/row_000090_byd_ane-byd-gods-eye-safety-self-driving-flaws-0325.md</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>35</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3414,7 +6012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3438,6 +6036,26 @@
           <t>scrape_status</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>relevance_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>semantic_match</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>processed_markdown_saved</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>processed_markdown_path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3447,7 +6065,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-25T13:30:49.484Z</t>
+          <t>2026-03-30T20:58:47.189Z</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3460,21 +6078,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.spglobal.com/automotive-insights/en/theme/electric-vehicle-industry</t>
+          <t>https://www.spglobal.com/automotive-insights/en/theme/automotive-consumer-trends</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-25T13:33:04.313Z</t>
+          <t>2026-03-30T21:14:43.402Z</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.spglobal.com/row_000003_automotive-insights_en_theme_electric-vehicle-industry.md</t>
+          <t>scraped_markdown/www.spglobal.com/row_000003_automotive-insights_en_theme_automotive-consumer-trends.md</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3482,21 +6114,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.spglobal.com/automotive-insights/en/blogs/2026/02/what-auto-marketers-and-dealers-need-to-know-about-the-dram-shortage</t>
+          <t>https://www.spglobal.com/automotive-insights/en/theme/automotive-industry-forecast/commercial-vehicle-market-data-insights</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-25T11:39:05.642Z</t>
+          <t>2026-03-30T21:23:26.477Z</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.spglobal.com/row_000004_automotive-insights_en_blogs_2026_02_what-auto-marketers-and-dealers-need-to-know-about-the-dram-shortage.md</t>
+          <t>scraped_markdown/www.spglobal.com/row_000004_automotive-insights_en_theme_automotive-industry-forecast_commercial-vehicle-market-data-insights.md</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3504,21 +6150,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.spglobal.com/automotive-insights/en/blogs/2026/03/ev-plans-us-cancellations-launches</t>
+          <t>https://www.spglobal.com/automotive-insights/en/theme/electric-vehicle-industry</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-25T13:02:45.519Z</t>
+          <t>2026-03-30T21:26:12.535Z</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.spglobal.com/row_000005_automotive-insights_en_blogs_2026_03_ev-plans-us-cancellations-launches.md</t>
+          <t>scraped_markdown/www.spglobal.com/row_000005_automotive-insights_en_theme_electric-vehicle-industry.md</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3526,28 +6186,164 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>https://www.spglobal.com/automotive-insights/en/blogs/2026/02/what-auto-marketers-and-dealers-need-to-know-about-the-dram-shortage</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-25T11:39:05.642Z</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.spglobal.com/row_000006_automotive-insights_en_blogs_2026_02_what-auto-marketers-and-dealers-need-to-know-about-the-dram-shortage.md</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/automotive-insights/en/blogs/2026/03/ev-plans-us-cancellations-launches</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-25T13:02:45.519Z</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.spglobal.com/row_000007_automotive-insights_en_blogs_2026_03_ev-plans-us-cancellations-launches.md</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/automotive-insights/en/blogs/us-auto-sales</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-30T17:11:20.945Z</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.spglobal.com/row_000008_automotive-insights_en_blogs_us-auto-sales.md</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>https://www.spglobal.com/automotive-insights/en/nada</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-03-26T18:13:19.712Z</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>scraped_markdown/www.spglobal.com/row_000006_automotive-insights_en_nada.md</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.spglobal.com/row_000009_automotive-insights_en_nada.md</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3560,7 +6356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3584,6 +6380,26 @@
           <t>scrape_status</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>relevance_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>semantic_match</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>processed_markdown_saved</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>processed_markdown_path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3606,6 +6422,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3628,6 +6458,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3650,6 +6494,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3672,6 +6530,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3694,6 +6566,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3716,6 +6602,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>65</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000007_news_valeo-breaks-ground-on-us225m-texas-sdv-plant_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3738,6 +6642,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3760,6 +6678,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3782,6 +6714,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>86</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000010_articles_holyvolts-wildcat-acquisition-tackles-wests-ev-battery-lag_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3804,6 +6754,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3826,6 +6790,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3848,6 +6826,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3870,6 +6862,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3892,6 +6898,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3914,6 +6934,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3936,6 +6970,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>92</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000017_news_autobrains-deploys-agentic-ai-for-adas-and-ad-systems_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3958,6 +7010,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>45</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3980,6 +7046,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4002,6 +7082,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4024,6 +7118,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E21" t="n">
+        <v>62</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000021_news_the-future-is-neutral-adds-ev-battery-recycling-to-autoloop_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4046,6 +7158,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E22" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4068,6 +7194,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4090,6 +7230,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4112,6 +7266,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E25" t="n">
+        <v>74</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000025_news_einride-publishes-safety-self-assessment-for-level-4-trucks_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4134,6 +7306,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E26" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4156,6 +7342,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4178,6 +7378,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4200,6 +7414,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4222,6 +7450,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E30" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4244,6 +7486,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4266,6 +7522,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E32" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4288,6 +7558,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E33" t="n">
+        <v>78</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4310,6 +7594,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E34" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4332,6 +7630,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E35" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4354,6 +7666,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E36" t="n">
+        <v>86</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000036_news_sany-launches-worlds-first-intelligent-hybrid-pump-truck_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4376,6 +7706,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4398,6 +7742,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4420,6 +7778,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E39" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4442,6 +7814,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E40" t="n">
+        <v>25</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4464,6 +7850,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E41" t="n">
+        <v>78</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000041_news_volvo-cars-wins-ajac-safety-award-for-adaptive-belt-tech_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4486,6 +7890,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4508,6 +7926,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E43" t="n">
+        <v>55</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4530,6 +7962,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E44" t="n">
+        <v>18</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4552,6 +7998,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4574,6 +8034,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4596,6 +8070,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4618,6 +8106,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E48" t="n">
+        <v>75</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000048_news_pony-ai-hits-first-gaap-profit-launches-europes-first-robotaxi_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4640,6 +8146,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E49" t="n">
+        <v>15</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4662,6 +8182,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E50" t="n">
+        <v>35</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4684,6 +8218,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4706,6 +8254,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4728,6 +8290,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E53" t="n">
+        <v>78</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000053_news_kentucky-researcher-wins-nsf-grant-for-av-safety-framework_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4750,6 +8330,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E54" t="n">
+        <v>35</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4772,6 +8366,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E55" t="n">
+        <v>55</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4794,6 +8402,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4816,6 +8438,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E57" t="n">
+        <v>72</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000057_news_amprius-lands-us21m-sicore-battery-deal-in-china_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4838,6 +8478,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4860,6 +8514,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4882,6 +8550,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E60" t="n">
+        <v>18</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4904,6 +8586,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4926,6 +8622,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4948,6 +8658,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E63" t="n">
+        <v>78</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000063_news_tmuk-burnaston-closes-the-loop-on-end-of-life-aluminium_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4970,6 +8698,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E64" t="n">
+        <v>55</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4992,6 +8734,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E65" t="n">
+        <v>12</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5014,6 +8770,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E66" t="n">
+        <v>15</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5036,6 +8806,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E67" t="n">
+        <v>35</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5058,6 +8842,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E68" t="n">
+        <v>15</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5080,6 +8878,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5102,6 +8914,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E70" t="n">
+        <v>25</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5124,6 +8950,24 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E71" t="n">
+        <v>85</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000071_news_google-open-sources-aaos-sdv-platform-for-automakers_processed.md</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5146,6 +8990,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5168,6 +9026,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E73" t="n">
+        <v>12</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5190,6 +9062,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E74" t="n">
+        <v>18</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5212,6 +9098,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E75" t="n">
+        <v>35</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5234,6 +9134,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E76" t="n">
+        <v>5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5256,6 +9170,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E77" t="n">
+        <v>58</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5278,6 +9206,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E78" t="n">
+        <v>8</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5300,6 +9242,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E79" t="n">
+        <v>10</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5322,6 +9278,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E80" t="n">
+        <v>18</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5344,6 +9314,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E81" t="n">
+        <v>45</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5366,6 +9350,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E82" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5388,6 +9386,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E83" t="n">
+        <v>45</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5410,6 +9422,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E84" t="n">
+        <v>10</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5432,6 +9458,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E85" t="n">
+        <v>25</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5454,6 +9494,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E86" t="n">
+        <v>35</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5476,6 +9530,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E87" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5498,6 +9566,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E88" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5520,6 +9602,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E89" t="n">
+        <v>35</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5542,6 +9638,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E90" t="n">
+        <v>18</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5564,6 +9674,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5586,6 +9710,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E92" t="n">
+        <v>8</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5608,6 +9746,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E93" t="n">
+        <v>5</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5630,6 +9782,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E94" t="n">
+        <v>5</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5652,6 +9818,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E95" t="n">
+        <v>12</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5674,6 +9854,20 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5696,65 +9890,115 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E97" t="n">
+        <v>35</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/media-specifications/</t>
+          <t>https://www.automotiveworld.com/news/lotus-technology-launches-for-me-hyper-suv-in-china/</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-03-25T17:23:22+00:00</t>
+          <t>2026-03-30T17:03:58+00:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000098_media-specifications.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000098_news_lotus-technology-launches-for-me-hyper-suv-in-china.md</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>success</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>72</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000098_news_lotus-technology-launches-for-me-hyper-suv-in-china_processed.md</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/editorial-calendar/</t>
+          <t>https://www.automotiveworld.com/news/schaeffler-develops-centralised-e-e-architecture-for-sdvs/</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-03-30T13:14:18+00:00</t>
+          <t>2026-03-30T17:06:39+00:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000099_editorial-calendar.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000099_news_schaeffler-develops-centralised-e-e-architecture-for-sdvs.md</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>success</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>85</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>processed_selected_markdown/www_automotiveworld_com_sitemap/www.automotiveworld.com/row_000099_news_schaeffler-develops-centralised-e-e-architecture-for-sdvs_processed.md</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/mp-files/</t>
+          <t>https://www.automotiveworld.com/news/volvo-cars-signs-mou-to-import-lynk-co-across-europe/</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-03-30T10:19:06+00:00</t>
+          <t>2026-03-30T18:32:04+00:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000100_mp-files.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000100_news_volvo-cars-signs-mou-to-import-lynk-co-across-europe.md</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5762,21 +10006,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E100" t="n">
+        <v>5</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/mp-files/volkswagen-group-profile-and-production-forecast-to-2030.xlsx/</t>
+          <t>https://www.automotiveworld.com/media-specifications/</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-03-30T10:19:06+00:00</t>
+          <t>2026-03-25T17:23:22+00:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000101_mp-files_volkswagen-group-profile-and-production-forecast-to-2030.xlsx.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000101_media-specifications.md</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5784,21 +10042,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/analysis/</t>
+          <t>https://www.automotiveworld.com/editorial-calendar/</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-03-30T14:36:04+00:00</t>
+          <t>2026-03-30T13:14:18+00:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000102_analysis.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000102_editorial-calendar.md</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5806,21 +10078,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E102" t="n">
+        <v>10</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/articles/</t>
+          <t>https://www.automotiveworld.com/mp-files/</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-03-27T08:31:45+00:00</t>
+          <t>2026-03-30T10:19:06+00:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000103_articles.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000103_mp-files.md</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5828,21 +10114,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/topics/autonomous-driving/</t>
+          <t>https://www.automotiveworld.com/mp-files/volkswagen-group-profile-and-production-forecast-to-2030.xlsx/</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-03-30T11:43:28+00:00</t>
+          <t>2026-03-30T10:19:06+00:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000104_topics_autonomous-driving.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000104_mp-files_volkswagen-group-profile-and-production-forecast-to-2030.xlsx.md</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5850,21 +10150,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/topics/commercial-vehicle/</t>
+          <t>https://www.automotiveworld.com/analysis/</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-03-30T11:52:28+00:00</t>
+          <t>2026-03-30T14:36:04+00:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000105_topics_commercial-vehicle.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000105_analysis.md</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5872,21 +10186,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/data/</t>
+          <t>https://www.automotiveworld.com/articles/</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-30T13:13:27+00:00</t>
+          <t>2026-03-27T08:31:45+00:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000106_data.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000106_articles.md</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5894,21 +10222,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/topics/e-mobility/</t>
+          <t>https://www.automotiveworld.com/topics/autonomous-driving/</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-30T14:45:41+00:00</t>
+          <t>2026-03-30T11:43:28+00:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000107_topics_e-mobility.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000107_topics_autonomous-driving.md</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5916,21 +10258,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/topics/manufacturing/</t>
+          <t>https://www.automotiveworld.com/topics/commercial-vehicle/</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-03-30T11:49:01+00:00</t>
+          <t>2026-03-30T11:52:28+00:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000108_topics_manufacturing.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000108_topics_commercial-vehicle.md</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5938,21 +10294,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E108" t="n">
+        <v>10</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/topics/markets/</t>
+          <t>https://www.automotiveworld.com/data/</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-03-30T14:45:41+00:00</t>
+          <t>2026-03-30T13:13:27+00:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000109_topics_markets.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000109_data.md</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5960,21 +10330,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E109" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/news/</t>
+          <t>https://www.automotiveworld.com/topics/e-mobility/</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-03-30T14:45:41+00:00</t>
+          <t>2026-03-30T18:32:04+00:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000110_news.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000110_topics_e-mobility.md</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5982,21 +10366,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E110" t="n">
+        <v>35</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/data/oem-outlooks/</t>
+          <t>https://www.automotiveworld.com/topics/manufacturing/</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-03-30T13:13:27+00:00</t>
+          <t>2026-03-30T11:49:01+00:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000111_data_oem-outlooks.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000111_topics_manufacturing.md</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6004,21 +10402,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/topics/oems/</t>
+          <t>https://www.automotiveworld.com/topics/markets/</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-30T14:45:41+00:00</t>
+          <t>2026-03-30T18:32:04+00:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000112_topics_oems.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000112_topics_markets.md</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6026,21 +10438,35 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.automotiveworld.com/topics/software-defined-vehicle/</t>
+          <t>https://www.automotiveworld.com/news/</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-30T12:13:35+00:00</t>
+          <t>2026-03-30T18:32:04+00:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000113_topics_software-defined-vehicle.md</t>
+          <t>scraped_markdown/www.automotiveworld.com/row_000113_news.md</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6048,28 +10474,164 @@
           <t>success</t>
         </is>
       </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>https://www.automotiveworld.com/data/oem-outlooks/</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-03-30T13:13:27+00:00</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.automotiveworld.com/row_000114_data_oem-outlooks.md</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://www.automotiveworld.com/topics/oems/</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-03-30T18:32:04+00:00</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.automotiveworld.com/row_000115_topics_oems.md</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>10</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://www.automotiveworld.com/topics/software-defined-vehicle/</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-03-30T17:06:39+00:00</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.automotiveworld.com/row_000116_topics_software-defined-vehicle.md</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>https://www.automotiveworld.com/file-tag/data/</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>2026-03-30T10:19:06+00:00</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>scraped_markdown/www.automotiveworld.com/row_000114_file-tag_data.md</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>scraped_markdown/www.automotiveworld.com/row_000117_file-tag_data.md</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>not_selected</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>not_saved</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
